--- a/categories_dump.xlsx
+++ b/categories_dump.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name=" 2025-12-13" sheetId="1" r:id="rId1"/>
+    <sheet name=" 2026-01-05" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J81"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -726,7 +726,7 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H12">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="I12" t="str">
         <v>2024-11-20 16:04:36</v>
@@ -737,13 +737,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v xml:space="preserve">    FLORAL 1 </v>
+        <v xml:space="preserve">    F8M</v>
       </c>
       <c r="B13" t="str">
-        <v xml:space="preserve">    FLR1</v>
+        <v xml:space="preserve">    F8M</v>
       </c>
       <c r="C13" t="str">
-        <v>588326</v>
+        <v>588330</v>
       </c>
       <c r="D13" t="str">
         <v>588320</v>
@@ -755,24 +755,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H13">
-        <v>30</v>
+        <v>435</v>
       </c>
       <c r="I13" t="str">
-        <v>2022-12-13 16:57:53</v>
+        <v>2023-11-17 16:01:41</v>
       </c>
       <c r="J13" t="str">
-        <v>/floral-1-pc588326.html</v>
+        <v>/f8m-pc588330.html</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v xml:space="preserve">    CLASSIC </v>
+        <v xml:space="preserve">    PLATY 1 </v>
       </c>
       <c r="B14" t="str">
-        <v xml:space="preserve">    CLN</v>
+        <v xml:space="preserve">    PLA1</v>
       </c>
       <c r="C14" t="str">
-        <v>588327</v>
+        <v>588329</v>
       </c>
       <c r="D14" t="str">
         <v>588320</v>
@@ -784,13 +784,13 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H14">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I14" t="str">
-        <v>2022-12-13 16:58:11</v>
+        <v>2022-12-13 16:58:54</v>
       </c>
       <c r="J14" t="str">
-        <v>/classic-pc588327.html</v>
+        <v>/platy-1-pc588329.html</v>
       </c>
     </row>
     <row r="15">
@@ -824,13 +824,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v xml:space="preserve">    F8B </v>
+        <v xml:space="preserve">    CLASSIC </v>
       </c>
       <c r="B16" t="str">
-        <v xml:space="preserve">    F8B</v>
+        <v xml:space="preserve">    CLN</v>
       </c>
       <c r="C16" t="str">
-        <v>591299</v>
+        <v>588327</v>
       </c>
       <c r="D16" t="str">
         <v>588320</v>
@@ -842,24 +842,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H16">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="I16" t="str">
-        <v>2023-10-11 15:46:22</v>
+        <v>2022-12-13 16:58:11</v>
       </c>
       <c r="J16" t="str">
-        <v>/f8b-pc591299.html</v>
+        <v>/classic-pc588327.html</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v xml:space="preserve">    SHAT 1 </v>
+        <v xml:space="preserve">    FX</v>
       </c>
       <c r="B17" t="str">
-        <v xml:space="preserve">    S1M</v>
+        <v xml:space="preserve">    FX</v>
       </c>
       <c r="C17" t="str">
-        <v>588325</v>
+        <v>591306</v>
       </c>
       <c r="D17" t="str">
         <v>588320</v>
@@ -871,24 +871,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H17">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="I17" t="str">
-        <v>2022-12-13 16:57:30</v>
+        <v>2024-09-18 10:01:23</v>
       </c>
       <c r="J17" t="str">
-        <v>/shat-1-pc588325.html</v>
+        <v>/fx-pc591306.html</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve">    FX</v>
+        <v xml:space="preserve">    FLORAL 1 </v>
       </c>
       <c r="B18" t="str">
-        <v xml:space="preserve">    FX</v>
+        <v xml:space="preserve">    FLR1</v>
       </c>
       <c r="C18" t="str">
-        <v>591306</v>
+        <v>588326</v>
       </c>
       <c r="D18" t="str">
         <v>588320</v>
@@ -900,24 +900,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H18">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="I18" t="str">
-        <v>2024-09-18 10:01:23</v>
+        <v>2022-12-13 16:57:53</v>
       </c>
       <c r="J18" t="str">
-        <v>/fx-pc591306.html</v>
+        <v>/floral-1-pc588326.html</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v xml:space="preserve">    GIRLY </v>
+        <v xml:space="preserve">    SHAT 1 </v>
       </c>
       <c r="B19" t="str">
-        <v xml:space="preserve">    GIR</v>
+        <v xml:space="preserve">    S1M</v>
       </c>
       <c r="C19" t="str">
-        <v>588324</v>
+        <v>588325</v>
       </c>
       <c r="D19" t="str">
         <v>588320</v>
@@ -929,24 +929,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H19">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="I19" t="str">
-        <v>2022-12-13 16:57:13</v>
+        <v>2022-12-13 16:57:30</v>
       </c>
       <c r="J19" t="str">
-        <v>/girly-pc588324.html</v>
+        <v>/shat-1-pc588325.html</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v xml:space="preserve">    CHICLY </v>
+        <v xml:space="preserve">    GIRLY </v>
       </c>
       <c r="B20" t="str">
-        <v xml:space="preserve">    CLY</v>
+        <v xml:space="preserve">    GIR</v>
       </c>
       <c r="C20" t="str">
-        <v>588323</v>
+        <v>588324</v>
       </c>
       <c r="D20" t="str">
         <v>588320</v>
@@ -958,24 +958,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H20">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="I20" t="str">
-        <v>2022-12-13 16:56:40</v>
+        <v>2022-12-13 16:57:13</v>
       </c>
       <c r="J20" t="str">
-        <v>/chicly-pc588323.html</v>
+        <v>/girly-pc588324.html</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v xml:space="preserve">    F7 TRACK </v>
+        <v xml:space="preserve">    CHICLY </v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">    F7T</v>
+        <v xml:space="preserve">    CLY</v>
       </c>
       <c r="C21" t="str">
-        <v>588322</v>
+        <v>588323</v>
       </c>
       <c r="D21" t="str">
         <v>588320</v>
@@ -987,24 +987,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H21">
-        <v>231</v>
+        <v>33</v>
       </c>
       <c r="I21" t="str">
-        <v>2022-12-13 16:56:19</v>
+        <v>2022-12-13 16:56:40</v>
       </c>
       <c r="J21" t="str">
-        <v>/f7-track-pc588322.html</v>
+        <v>/chicly-pc588323.html</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v xml:space="preserve">    CUSTOM </v>
+        <v xml:space="preserve">    F7 TRACK </v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">    F7P</v>
+        <v xml:space="preserve">    F7T</v>
       </c>
       <c r="C22" t="str">
-        <v>588321</v>
+        <v>588322</v>
       </c>
       <c r="D22" t="str">
         <v>588320</v>
@@ -1016,24 +1016,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H22">
-        <v>4</v>
+        <v>231</v>
       </c>
       <c r="I22" t="str">
-        <v>2022-12-13 16:55:58</v>
+        <v>2022-12-13 16:56:19</v>
       </c>
       <c r="J22" t="str">
-        <v>/custom-pc588321.html</v>
+        <v>/f7-track-pc588322.html</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v xml:space="preserve">    F7 CONTINEW </v>
+        <v xml:space="preserve">    CUSTOM </v>
       </c>
       <c r="B23" t="str">
-        <v xml:space="preserve">    F7N</v>
+        <v xml:space="preserve">    F7P</v>
       </c>
       <c r="C23" t="str">
-        <v>588331</v>
+        <v>588321</v>
       </c>
       <c r="D23" t="str">
         <v>588320</v>
@@ -1045,53 +1045,53 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H23">
-        <v>323</v>
+        <v>4</v>
       </c>
       <c r="I23" t="str">
-        <v>2022-12-13 16:59:38</v>
+        <v>2022-12-13 16:55:58</v>
       </c>
       <c r="J23" t="str">
-        <v>/f7-continew-pc588331.html</v>
+        <v>/custom-pc588321.html</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v xml:space="preserve">    F5 </v>
+        <v xml:space="preserve">    F6 </v>
       </c>
       <c r="B24" t="str">
-        <v xml:space="preserve">    F5</v>
+        <v xml:space="preserve">    F6</v>
       </c>
       <c r="C24" t="str">
-        <v>588332</v>
+        <v>588333</v>
       </c>
       <c r="D24" t="str">
         <v>588320</v>
       </c>
       <c r="E24" t="str">
-        <v>Ẩn</v>
+        <v>Hoạt động</v>
       </c>
       <c r="G24" t="str">
         <v>Không hiển thị</v>
       </c>
       <c r="H24">
-        <v>405</v>
+        <v>328</v>
       </c>
       <c r="I24" t="str">
-        <v>2022-12-13 16:59:57</v>
+        <v>2022-12-13 17:00:22</v>
       </c>
       <c r="J24" t="str">
-        <v>/f5-pc588332.html</v>
+        <v>/f6-pc588333.html</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v xml:space="preserve">    F6 </v>
+        <v xml:space="preserve">    F6 SPORT </v>
       </c>
       <c r="B25" t="str">
-        <v xml:space="preserve">    F6</v>
+        <v xml:space="preserve">    F6S</v>
       </c>
       <c r="C25" t="str">
-        <v>588333</v>
+        <v>588334</v>
       </c>
       <c r="D25" t="str">
         <v>588320</v>
@@ -1103,24 +1103,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H25">
-        <v>328</v>
+        <v>1020</v>
       </c>
       <c r="I25" t="str">
-        <v>2022-12-13 17:00:22</v>
+        <v>2022-12-13 17:00:38</v>
       </c>
       <c r="J25" t="str">
-        <v>/f6-pc588333.html</v>
+        <v>/f6-sport-pc588334.html</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v xml:space="preserve">    F6 SPORT </v>
+        <v xml:space="preserve">    F7 RACING </v>
       </c>
       <c r="B26" t="str">
-        <v xml:space="preserve">    F6S</v>
+        <v xml:space="preserve">    F7R</v>
       </c>
       <c r="C26" t="str">
-        <v>588334</v>
+        <v>588335</v>
       </c>
       <c r="D26" t="str">
         <v>588320</v>
@@ -1132,24 +1132,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H26">
-        <v>1020</v>
+        <v>725</v>
       </c>
       <c r="I26" t="str">
-        <v>2022-12-13 17:00:38</v>
+        <v>2022-12-13 17:00:59</v>
       </c>
       <c r="J26" t="str">
-        <v>/f6-sport-pc588334.html</v>
+        <v>/f7-racing-pc588335.html</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v xml:space="preserve">    F7 RACING </v>
+        <v xml:space="preserve">    F8B </v>
       </c>
       <c r="B27" t="str">
-        <v xml:space="preserve">    F7R</v>
+        <v xml:space="preserve">    F8B</v>
       </c>
       <c r="C27" t="str">
-        <v>588335</v>
+        <v>591299</v>
       </c>
       <c r="D27" t="str">
         <v>588320</v>
@@ -1161,24 +1161,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H27">
-        <v>708</v>
+        <v>179</v>
       </c>
       <c r="I27" t="str">
-        <v>2022-12-13 17:00:59</v>
+        <v>2023-10-11 15:46:22</v>
       </c>
       <c r="J27" t="str">
-        <v>/f7-racing-pc588335.html</v>
+        <v>/f8b-pc591299.html</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v xml:space="preserve">    PLATY 1 </v>
+        <v xml:space="preserve">    F7 CONTINEW </v>
       </c>
       <c r="B28" t="str">
-        <v xml:space="preserve">    PLA1</v>
+        <v xml:space="preserve">    F7N</v>
       </c>
       <c r="C28" t="str">
-        <v>588329</v>
+        <v>588331</v>
       </c>
       <c r="D28" t="str">
         <v>588320</v>
@@ -1190,13 +1190,13 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H28">
-        <v>92</v>
+        <v>323</v>
       </c>
       <c r="I28" t="str">
-        <v>2022-12-13 16:58:54</v>
+        <v>2022-12-13 16:59:38</v>
       </c>
       <c r="J28" t="str">
-        <v>/platy-1-pc588329.html</v>
+        <v>/f7-continew-pc588331.html</v>
       </c>
     </row>
     <row r="29">
@@ -1288,31 +1288,31 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v xml:space="preserve">    F8M</v>
+        <v xml:space="preserve">    F5 </v>
       </c>
       <c r="B32" t="str">
-        <v xml:space="preserve">    F8M</v>
+        <v xml:space="preserve">    F5</v>
       </c>
       <c r="C32" t="str">
-        <v>588330</v>
+        <v>588332</v>
       </c>
       <c r="D32" t="str">
         <v>588320</v>
       </c>
       <c r="E32" t="str">
-        <v>Hoạt động</v>
+        <v>Ẩn</v>
       </c>
       <c r="G32" t="str">
         <v>Không hiển thị</v>
       </c>
       <c r="H32">
-        <v>435</v>
+        <v>405</v>
       </c>
       <c r="I32" t="str">
-        <v>2023-11-17 16:01:41</v>
+        <v>2022-12-13 16:59:57</v>
       </c>
       <c r="J32" t="str">
-        <v>/f8m-pc588330.html</v>
+        <v>/f5-pc588332.html</v>
       </c>
     </row>
     <row r="33">
@@ -1393,7 +1393,7 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H35">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I35" t="str">
         <v>2025-05-22 16:21:58</v>
@@ -1462,13 +1462,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">    CLASSIC 1 </v>
+        <v xml:space="preserve">    CLASS7</v>
       </c>
       <c r="B38" t="str">
-        <v xml:space="preserve">    SND1</v>
+        <v xml:space="preserve">    S7C</v>
       </c>
       <c r="C38" t="str">
-        <v>588343</v>
+        <v>591326</v>
       </c>
       <c r="D38" t="str">
         <v>588342</v>
@@ -1480,24 +1480,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H38">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="I38" t="str">
-        <v>2022-12-13 17:27:01</v>
+        <v>2025-12-17 15:04:07</v>
       </c>
       <c r="J38" t="str">
-        <v>/classic-1-pc588343.html</v>
+        <v>/class7-pc591326.html</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v xml:space="preserve">    CHUNKY 1 </v>
+        <v xml:space="preserve">    S4 EZI</v>
       </c>
       <c r="B39" t="str">
-        <v xml:space="preserve">    CHN1</v>
+        <v xml:space="preserve">    S4EZI</v>
       </c>
       <c r="C39" t="str">
-        <v>588344</v>
+        <v>591327</v>
       </c>
       <c r="D39" t="str">
         <v>588342</v>
@@ -1509,13 +1509,13 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H39">
-        <v>188</v>
+        <v>26</v>
       </c>
       <c r="I39" t="str">
-        <v>2022-12-13 17:28:15</v>
+        <v>2026-01-05 10:57:56</v>
       </c>
       <c r="J39" t="str">
-        <v>/chunky-1-pc588344.html</v>
+        <v>/s4-ezi-pc591327.html</v>
       </c>
     </row>
     <row r="40">
@@ -1549,45 +1549,45 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v xml:space="preserve">  KID SANDALS</v>
+        <v xml:space="preserve">    CLASSIC 1 </v>
       </c>
       <c r="B41" t="str">
-        <v xml:space="preserve">  KIDSANDALS</v>
+        <v xml:space="preserve">    SND1</v>
       </c>
       <c r="C41" t="str">
-        <v>588316</v>
+        <v>588343</v>
       </c>
       <c r="D41" t="str">
-        <v>588214</v>
+        <v>588342</v>
       </c>
       <c r="E41" t="str">
         <v>Hoạt động</v>
       </c>
-      <c r="F41">
-        <v>4</v>
-      </c>
       <c r="G41" t="str">
         <v>Không hiển thị</v>
       </c>
+      <c r="H41">
+        <v>399</v>
+      </c>
       <c r="I41" t="str">
-        <v>2024-01-17 16:15:34</v>
+        <v>2022-12-13 17:27:01</v>
       </c>
       <c r="J41" t="str">
-        <v>/kid-sandals-pc588316.html</v>
+        <v>/classic-1-pc588343.html</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v xml:space="preserve">    PLATY 2 KID</v>
+        <v xml:space="preserve">    CHUNKY 1 </v>
       </c>
       <c r="B42" t="str">
-        <v xml:space="preserve">    PLA2KID</v>
+        <v xml:space="preserve">    CHN1</v>
       </c>
       <c r="C42" t="str">
-        <v>591300</v>
+        <v>588344</v>
       </c>
       <c r="D42" t="str">
-        <v>588316</v>
+        <v>588342</v>
       </c>
       <c r="E42" t="str">
         <v>Hoạt động</v>
@@ -1596,56 +1596,56 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H42">
-        <v>7</v>
+        <v>188</v>
       </c>
       <c r="I42" t="str">
-        <v>2023-12-07 14:43:20</v>
+        <v>2022-12-13 17:28:15</v>
       </c>
       <c r="J42" t="str">
-        <v>/platy-2-kid-pc591300.html</v>
+        <v>/chunky-1-pc588344.html</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v xml:space="preserve">    LITTLE FX</v>
+        <v xml:space="preserve">  KID SNEAKERS</v>
       </c>
       <c r="B43" t="str">
-        <v xml:space="preserve">    LITX</v>
+        <v xml:space="preserve">  KIDSNEAKERS</v>
       </c>
       <c r="C43" t="str">
-        <v>591314</v>
+        <v>591315</v>
       </c>
       <c r="D43" t="str">
-        <v>588316</v>
+        <v>588214</v>
       </c>
       <c r="E43" t="str">
         <v>Hoạt động</v>
       </c>
+      <c r="F43">
+        <v>4</v>
+      </c>
       <c r="G43" t="str">
         <v>Không hiển thị</v>
       </c>
-      <c r="H43">
-        <v>30</v>
-      </c>
       <c r="I43" t="str">
-        <v>2025-04-01 10:33:20</v>
+        <v>2025-06-21 17:21:37</v>
       </c>
       <c r="J43" t="str">
-        <v>/little-fx-pc591314.html</v>
+        <v>/kid-sneakers-pc591315.html</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v xml:space="preserve">    LITTLE 6</v>
+        <v xml:space="preserve">    LITTLE SUKE</v>
       </c>
       <c r="B44" t="str">
-        <v xml:space="preserve">    LIT6</v>
+        <v xml:space="preserve">    LITSUK</v>
       </c>
       <c r="C44" t="str">
-        <v>591303</v>
+        <v>591316</v>
       </c>
       <c r="D44" t="str">
-        <v>588316</v>
+        <v>591315</v>
       </c>
       <c r="E44" t="str">
         <v>Hoạt động</v>
@@ -1654,27 +1654,27 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H44">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="I44" t="str">
-        <v>2024-07-08 13:52:49</v>
+        <v>2025-04-23 14:18:35</v>
       </c>
       <c r="J44" t="str">
-        <v>/little-6-pc591303.html</v>
+        <v>/little-suke-pc591316.html</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v xml:space="preserve">    LITTLE 8</v>
+        <v xml:space="preserve">    Little Dreamie</v>
       </c>
       <c r="B45" t="str">
-        <v xml:space="preserve">    LIT8</v>
+        <v xml:space="preserve">    LITDRE</v>
       </c>
       <c r="C45" t="str">
-        <v>591304</v>
+        <v>591320</v>
       </c>
       <c r="D45" t="str">
-        <v>588316</v>
+        <v>591315</v>
       </c>
       <c r="E45" t="str">
         <v>Hoạt động</v>
@@ -1683,53 +1683,53 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H45">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="I45" t="str">
-        <v>2024-08-05 15:38:59</v>
+        <v>2025-06-10 16:37:14</v>
       </c>
       <c r="J45" t="str">
-        <v>/little-8-pc591304.html</v>
+        <v>/little-dreamie-pc591320.html</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v xml:space="preserve">    LITTLE 3 </v>
+        <v xml:space="preserve">  KID SANDALS</v>
       </c>
       <c r="B46" t="str">
-        <v xml:space="preserve">    LIT3</v>
+        <v xml:space="preserve">  KIDSANDALS</v>
       </c>
       <c r="C46" t="str">
-        <v>591295</v>
+        <v>588316</v>
       </c>
       <c r="D46" t="str">
-        <v>588316</v>
+        <v>588214</v>
       </c>
       <c r="E46" t="str">
         <v>Hoạt động</v>
       </c>
+      <c r="F46">
+        <v>4</v>
+      </c>
       <c r="G46" t="str">
         <v>Không hiển thị</v>
       </c>
-      <c r="H46">
-        <v>35</v>
-      </c>
       <c r="I46" t="str">
-        <v>2023-08-11 14:40:36</v>
+        <v>2024-01-17 16:15:34</v>
       </c>
       <c r="J46" t="str">
-        <v>/little-3-pc591295.html</v>
+        <v>/kid-sandals-pc588316.html</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v xml:space="preserve">    PLATY 1 KID </v>
+        <v xml:space="preserve">    PLATY 2 KID</v>
       </c>
       <c r="B47" t="str">
-        <v xml:space="preserve">    PLA1KID</v>
+        <v xml:space="preserve">    PLA2KID</v>
       </c>
       <c r="C47" t="str">
-        <v>591298</v>
+        <v>591300</v>
       </c>
       <c r="D47" t="str">
         <v>588316</v>
@@ -1741,24 +1741,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H47">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I47" t="str">
-        <v>2023-09-14 09:33:20</v>
+        <v>2023-12-07 14:43:20</v>
       </c>
       <c r="J47" t="str">
-        <v>/platy-1-kid-pc591298.html</v>
+        <v>/platy-2-kid-pc591300.html</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v xml:space="preserve">    LITTLE 4</v>
+        <v xml:space="preserve">    LITTLE FX</v>
       </c>
       <c r="B48" t="str">
-        <v xml:space="preserve">    LIT4</v>
+        <v xml:space="preserve">    LITX</v>
       </c>
       <c r="C48" t="str">
-        <v>591313</v>
+        <v>591314</v>
       </c>
       <c r="D48" t="str">
         <v>588316</v>
@@ -1770,24 +1770,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H48">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I48" t="str">
-        <v>2025-01-13 15:05:33</v>
+        <v>2025-04-01 10:33:20</v>
       </c>
       <c r="J48" t="str">
-        <v>/little-4-pc591313.html</v>
+        <v>/little-fx-pc591314.html</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v xml:space="preserve">    F7 KID</v>
+        <v xml:space="preserve">    LITTLE 4</v>
       </c>
       <c r="B49" t="str">
-        <v xml:space="preserve">    F7KID</v>
+        <v xml:space="preserve">    LIT4</v>
       </c>
       <c r="C49" t="str">
-        <v>588319</v>
+        <v>591313</v>
       </c>
       <c r="D49" t="str">
         <v>588316</v>
@@ -1799,24 +1799,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H49">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="I49" t="str">
-        <v>2022-12-13 16:53:03</v>
+        <v>2025-01-13 15:05:33</v>
       </c>
       <c r="J49" t="str">
-        <v>/f7-kid-pc588319.html</v>
+        <v>/little-4-pc591313.html</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v xml:space="preserve">    KID 2018 </v>
+        <v xml:space="preserve">    LITTLE 6</v>
       </c>
       <c r="B50" t="str">
-        <v xml:space="preserve">    KID 2018</v>
+        <v xml:space="preserve">    LIT6</v>
       </c>
       <c r="C50" t="str">
-        <v>588318</v>
+        <v>591303</v>
       </c>
       <c r="D50" t="str">
         <v>588316</v>
@@ -1828,24 +1828,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H50">
-        <v>143</v>
+        <v>70</v>
       </c>
       <c r="I50" t="str">
-        <v>2022-12-13 16:52:39</v>
+        <v>2024-07-08 13:52:49</v>
       </c>
       <c r="J50" t="str">
-        <v>/kid-2018-pc588318.html</v>
+        <v>/little-6-pc591303.html</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v xml:space="preserve">    LITTLE 1 </v>
+        <v xml:space="preserve">    LITTLE 8</v>
       </c>
       <c r="B51" t="str">
-        <v xml:space="preserve">    LIT1</v>
+        <v xml:space="preserve">    LIT8</v>
       </c>
       <c r="C51" t="str">
-        <v>588317</v>
+        <v>591304</v>
       </c>
       <c r="D51" t="str">
         <v>588316</v>
@@ -1857,24 +1857,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H51">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I51" t="str">
-        <v>2022-12-13 16:52:18</v>
+        <v>2024-08-05 15:38:59</v>
       </c>
       <c r="J51" t="str">
-        <v>/little-1-pc588317.html</v>
+        <v>/little-8-pc591304.html</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v xml:space="preserve">    LITTLE 2 </v>
+        <v xml:space="preserve">    F7 KID</v>
       </c>
       <c r="B52" t="str">
-        <v xml:space="preserve">    LIT2</v>
+        <v xml:space="preserve">    F7KID</v>
       </c>
       <c r="C52" t="str">
-        <v>591291</v>
+        <v>588319</v>
       </c>
       <c r="D52" t="str">
         <v>588316</v>
@@ -1886,24 +1886,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H52">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="I52" t="str">
-        <v>2023-04-20 15:55:58</v>
+        <v>2022-12-13 16:53:03</v>
       </c>
       <c r="J52" t="str">
-        <v>/little-2-pc591291.html</v>
+        <v>/f7-kid-pc588319.html</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v xml:space="preserve">    LITTLE F6S </v>
+        <v xml:space="preserve">    KID 2018 </v>
       </c>
       <c r="B53" t="str">
-        <v xml:space="preserve">    LITF6S</v>
+        <v xml:space="preserve">    KID 2018</v>
       </c>
       <c r="C53" t="str">
-        <v>591296</v>
+        <v>588318</v>
       </c>
       <c r="D53" t="str">
         <v>588316</v>
@@ -1915,56 +1915,56 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H53">
-        <v>49</v>
+        <v>143</v>
       </c>
       <c r="I53" t="str">
-        <v>2023-08-11 14:41:26</v>
+        <v>2022-12-13 16:52:39</v>
       </c>
       <c r="J53" t="str">
-        <v>/little-f6s-pc591296.html</v>
+        <v>/kid-2018-pc588318.html</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v xml:space="preserve">  KID SNEAKERS</v>
+        <v xml:space="preserve">    LITTLE 1 </v>
       </c>
       <c r="B54" t="str">
-        <v xml:space="preserve">  KIDSNEAKERS</v>
+        <v xml:space="preserve">    LIT1</v>
       </c>
       <c r="C54" t="str">
-        <v>591315</v>
+        <v>588317</v>
       </c>
       <c r="D54" t="str">
-        <v>588214</v>
+        <v>588316</v>
       </c>
       <c r="E54" t="str">
         <v>Hoạt động</v>
       </c>
-      <c r="F54">
-        <v>4</v>
-      </c>
       <c r="G54" t="str">
         <v>Không hiển thị</v>
       </c>
+      <c r="H54">
+        <v>77</v>
+      </c>
       <c r="I54" t="str">
-        <v>2025-06-21 17:21:37</v>
+        <v>2022-12-13 16:52:18</v>
       </c>
       <c r="J54" t="str">
-        <v>/kid-sneakers-pc591315.html</v>
+        <v>/little-1-pc588317.html</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v xml:space="preserve">    LITTLE SUKE</v>
+        <v xml:space="preserve">    LITTLE 2 </v>
       </c>
       <c r="B55" t="str">
-        <v xml:space="preserve">    LITSUK</v>
+        <v xml:space="preserve">    LIT2</v>
       </c>
       <c r="C55" t="str">
-        <v>591316</v>
+        <v>591291</v>
       </c>
       <c r="D55" t="str">
-        <v>591315</v>
+        <v>588316</v>
       </c>
       <c r="E55" t="str">
         <v>Hoạt động</v>
@@ -1973,27 +1973,27 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H55">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I55" t="str">
-        <v>2025-04-23 14:18:35</v>
+        <v>2023-04-20 15:55:58</v>
       </c>
       <c r="J55" t="str">
-        <v>/little-suke-pc591316.html</v>
+        <v>/little-2-pc591291.html</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v xml:space="preserve">    Little Dreamie</v>
+        <v xml:space="preserve">    LITTLE 3 </v>
       </c>
       <c r="B56" t="str">
-        <v xml:space="preserve">    LITDRE</v>
+        <v xml:space="preserve">    LIT3</v>
       </c>
       <c r="C56" t="str">
-        <v>591320</v>
+        <v>591295</v>
       </c>
       <c r="D56" t="str">
-        <v>591315</v>
+        <v>588316</v>
       </c>
       <c r="E56" t="str">
         <v>Hoạt động</v>
@@ -2002,56 +2002,56 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H56">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I56" t="str">
-        <v>2025-06-10 16:37:14</v>
+        <v>2023-08-11 14:40:36</v>
       </c>
       <c r="J56" t="str">
-        <v>/little-dreamie-pc591320.html</v>
+        <v>/little-3-pc591295.html</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v xml:space="preserve">  SLIDES</v>
+        <v xml:space="preserve">    LITTLE F6S </v>
       </c>
       <c r="B57" t="str">
-        <v xml:space="preserve">  SLIDES</v>
+        <v xml:space="preserve">    LITF6S</v>
       </c>
       <c r="C57" t="str">
-        <v>588336</v>
+        <v>591296</v>
       </c>
       <c r="D57" t="str">
-        <v>588214</v>
+        <v>588316</v>
       </c>
       <c r="E57" t="str">
         <v>Hoạt động</v>
       </c>
-      <c r="F57">
-        <v>5</v>
-      </c>
       <c r="G57" t="str">
         <v>Không hiển thị</v>
       </c>
+      <c r="H57">
+        <v>49</v>
+      </c>
       <c r="I57" t="str">
-        <v>2024-01-17 16:15:46</v>
+        <v>2023-08-11 14:41:26</v>
       </c>
       <c r="J57" t="str">
-        <v>/slides-pc588336.html</v>
+        <v>/little-f6s-pc591296.html</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v xml:space="preserve">    TRENDY 5</v>
+        <v xml:space="preserve">    PLATY 1 KID </v>
       </c>
       <c r="B58" t="str">
-        <v xml:space="preserve">    TRE5</v>
+        <v xml:space="preserve">    PLA1KID</v>
       </c>
       <c r="C58" t="str">
-        <v>591302</v>
+        <v>591298</v>
       </c>
       <c r="D58" t="str">
-        <v>588336</v>
+        <v>588316</v>
       </c>
       <c r="E58" t="str">
         <v>Hoạt động</v>
@@ -2060,53 +2060,53 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H58">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="I58" t="str">
-        <v>2023-12-19 08:21:58</v>
+        <v>2023-09-14 09:33:20</v>
       </c>
       <c r="J58" t="str">
-        <v>/trendy-5-pc591302.html</v>
+        <v>/platy-1-kid-pc591298.html</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v xml:space="preserve">    TRENDY 7</v>
+        <v xml:space="preserve">  SLIDES</v>
       </c>
       <c r="B59" t="str">
-        <v xml:space="preserve">    TRE7</v>
+        <v xml:space="preserve">  SLIDES</v>
       </c>
       <c r="C59" t="str">
-        <v>591318</v>
+        <v>588336</v>
       </c>
       <c r="D59" t="str">
-        <v>588336</v>
+        <v>588214</v>
       </c>
       <c r="E59" t="str">
         <v>Hoạt động</v>
       </c>
+      <c r="F59">
+        <v>5</v>
+      </c>
       <c r="G59" t="str">
         <v>Không hiển thị</v>
       </c>
-      <c r="H59">
-        <v>50</v>
-      </c>
       <c r="I59" t="str">
-        <v>2025-05-22 16:20:05</v>
+        <v>2024-01-17 16:15:46</v>
       </c>
       <c r="J59" t="str">
-        <v>/trendy-7-pc591318.html</v>
+        <v>/slides-pc588336.html</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v xml:space="preserve">    TRENDY 6</v>
+        <v xml:space="preserve">    TRENDY 5</v>
       </c>
       <c r="B60" t="str">
-        <v xml:space="preserve">    TRE6</v>
+        <v xml:space="preserve">    TRE5</v>
       </c>
       <c r="C60" t="str">
-        <v>591322</v>
+        <v>591302</v>
       </c>
       <c r="D60" t="str">
         <v>588336</v>
@@ -2118,24 +2118,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H60">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="I60" t="str">
-        <v>2025-07-09 10:44:36</v>
+        <v>2023-12-19 08:21:58</v>
       </c>
       <c r="J60" t="str">
-        <v>/trendy-6-pc591322.html</v>
+        <v>/trendy-5-pc591302.html</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v xml:space="preserve">    MULEZY</v>
+        <v xml:space="preserve">    TRENDY 7</v>
       </c>
       <c r="B61" t="str">
-        <v xml:space="preserve">    MUL</v>
+        <v xml:space="preserve">    TRE7</v>
       </c>
       <c r="C61" t="str">
-        <v>591323</v>
+        <v>591318</v>
       </c>
       <c r="D61" t="str">
         <v>588336</v>
@@ -2147,24 +2147,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H61">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="I61" t="str">
-        <v>2025-07-10 15:16:34</v>
+        <v>2025-05-22 16:20:05</v>
       </c>
       <c r="J61" t="str">
-        <v>/mulezy-pc591323.html</v>
+        <v>/trendy-7-pc591318.html</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v xml:space="preserve">    MULE CHIC</v>
+        <v xml:space="preserve">    TRENDY 6</v>
       </c>
       <c r="B62" t="str">
-        <v xml:space="preserve">    MLC</v>
+        <v xml:space="preserve">    TRE6</v>
       </c>
       <c r="C62" t="str">
-        <v>591325</v>
+        <v>591322</v>
       </c>
       <c r="D62" t="str">
         <v>588336</v>
@@ -2176,24 +2176,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H62">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I62" t="str">
-        <v>2025-12-01 10:21:06</v>
+        <v>2025-07-09 10:44:36</v>
       </c>
       <c r="J62" t="str">
-        <v>/mule-chic-pc591325.html</v>
+        <v>/trendy-6-pc591322.html</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v xml:space="preserve">    TRENDY 1 </v>
+        <v xml:space="preserve">    MULEZY</v>
       </c>
       <c r="B63" t="str">
-        <v xml:space="preserve">    TRE1</v>
+        <v xml:space="preserve">    MUL</v>
       </c>
       <c r="C63" t="str">
-        <v>588337</v>
+        <v>591323</v>
       </c>
       <c r="D63" t="str">
         <v>588336</v>
@@ -2205,24 +2205,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H63">
-        <v>668</v>
+        <v>33</v>
       </c>
       <c r="I63" t="str">
-        <v>2022-12-13 17:12:48</v>
+        <v>2025-07-10 15:16:34</v>
       </c>
       <c r="J63" t="str">
-        <v>/trendy-1-pc588337.html</v>
+        <v>/mulezy-pc591323.html</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v xml:space="preserve">    TRENDY 2  </v>
+        <v xml:space="preserve">    MULE CHIC</v>
       </c>
       <c r="B64" t="str">
-        <v xml:space="preserve">    TRE2</v>
+        <v xml:space="preserve">    MLC</v>
       </c>
       <c r="C64" t="str">
-        <v>588338</v>
+        <v>591325</v>
       </c>
       <c r="D64" t="str">
         <v>588336</v>
@@ -2234,24 +2234,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H64">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="I64" t="str">
-        <v>2022-12-13 17:13:02</v>
+        <v>2025-12-01 10:21:06</v>
       </c>
       <c r="J64" t="str">
-        <v>/trendy-2-pc588338.html</v>
+        <v>/mule-chic-pc591325.html</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v xml:space="preserve">    TRENDY 3 </v>
+        <v xml:space="preserve">    TRENDY 1 </v>
       </c>
       <c r="B65" t="str">
-        <v xml:space="preserve">    TRE3</v>
+        <v xml:space="preserve">    TRE1</v>
       </c>
       <c r="C65" t="str">
-        <v>588339</v>
+        <v>588337</v>
       </c>
       <c r="D65" t="str">
         <v>588336</v>
@@ -2263,24 +2263,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H65">
-        <v>247</v>
+        <v>668</v>
       </c>
       <c r="I65" t="str">
-        <v>2022-12-13 17:13:17</v>
+        <v>2022-12-13 17:12:48</v>
       </c>
       <c r="J65" t="str">
-        <v>/trendy-3-pc588339.html</v>
+        <v>/trendy-1-pc588337.html</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v xml:space="preserve">    FLIPPY </v>
+        <v xml:space="preserve">    TRENDY 2  </v>
       </c>
       <c r="B66" t="str">
-        <v xml:space="preserve">    FLP</v>
+        <v xml:space="preserve">    TRE2</v>
       </c>
       <c r="C66" t="str">
-        <v>588340</v>
+        <v>588338</v>
       </c>
       <c r="D66" t="str">
         <v>588336</v>
@@ -2292,53 +2292,53 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H66">
-        <v>128</v>
+        <v>199</v>
       </c>
       <c r="I66" t="str">
-        <v>2022-12-13 17:13:36</v>
+        <v>2022-12-13 17:13:02</v>
       </c>
       <c r="J66" t="str">
-        <v>/flippy-pc588340.html</v>
+        <v>/trendy-2-pc588338.html</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v xml:space="preserve">    TỔ ONG </v>
+        <v xml:space="preserve">    TRENDY 3 </v>
       </c>
       <c r="B67" t="str">
-        <v xml:space="preserve">    TON</v>
+        <v xml:space="preserve">    TRE3</v>
       </c>
       <c r="C67" t="str">
-        <v>588341</v>
+        <v>588339</v>
       </c>
       <c r="D67" t="str">
         <v>588336</v>
       </c>
       <c r="E67" t="str">
-        <v>Ẩn</v>
+        <v>Hoạt động</v>
       </c>
       <c r="G67" t="str">
         <v>Không hiển thị</v>
       </c>
       <c r="H67">
-        <v>61</v>
+        <v>247</v>
       </c>
       <c r="I67" t="str">
-        <v>2022-12-13 17:13:52</v>
+        <v>2022-12-13 17:13:17</v>
       </c>
       <c r="J67" t="str">
-        <v>/to-ong-pc588341.html</v>
+        <v>/trendy-3-pc588339.html</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v xml:space="preserve">    TRENDY 4 </v>
+        <v xml:space="preserve">    FLIPPY </v>
       </c>
       <c r="B68" t="str">
-        <v xml:space="preserve">    TRE4</v>
+        <v xml:space="preserve">    FLP</v>
       </c>
       <c r="C68" t="str">
-        <v>591292</v>
+        <v>588340</v>
       </c>
       <c r="D68" t="str">
         <v>588336</v>
@@ -2350,56 +2350,56 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H68">
-        <v>211</v>
+        <v>128</v>
       </c>
       <c r="I68" t="str">
-        <v>2023-04-20 15:58:40</v>
+        <v>2022-12-13 17:13:36</v>
       </c>
       <c r="J68" t="str">
-        <v>/trendy-4-pc591292.html</v>
+        <v>/flippy-pc588340.html</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>HATS</v>
+        <v xml:space="preserve">    TỔ ONG </v>
       </c>
       <c r="B69" t="str">
-        <v>HATS</v>
+        <v xml:space="preserve">    TON</v>
       </c>
       <c r="C69" t="str">
-        <v>543055</v>
+        <v>588341</v>
+      </c>
+      <c r="D69" t="str">
+        <v>588336</v>
       </c>
       <c r="E69" t="str">
-        <v>Hoạt động</v>
-      </c>
-      <c r="F69">
-        <v>7</v>
+        <v>Ẩn</v>
       </c>
       <c r="G69" t="str">
         <v>Không hiển thị</v>
       </c>
       <c r="H69">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="I69" t="str">
-        <v>2024-01-17 16:16:29</v>
+        <v>2022-12-13 17:13:52</v>
       </c>
       <c r="J69" t="str">
-        <v>/hats-pc543055.html</v>
+        <v>/to-ong-pc588341.html</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v xml:space="preserve">  BALL CAPS </v>
+        <v xml:space="preserve">    TRENDY 4 </v>
       </c>
       <c r="B70" t="str">
-        <v xml:space="preserve">  BALL CAPS</v>
+        <v xml:space="preserve">    TRE4</v>
       </c>
       <c r="C70" t="str">
-        <v>588418</v>
+        <v>591292</v>
       </c>
       <c r="D70" t="str">
-        <v>543055</v>
+        <v>588336</v>
       </c>
       <c r="E70" t="str">
         <v>Hoạt động</v>
@@ -2408,82 +2408,85 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H70">
-        <v>38</v>
+        <v>211</v>
       </c>
       <c r="I70" t="str">
-        <v>2022-12-16 09:16:06</v>
+        <v>2023-04-20 15:58:40</v>
       </c>
       <c r="J70" t="str">
-        <v>/ball-caps-pc588418.html</v>
+        <v>/trendy-4-pc591292.html</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v xml:space="preserve">  BUCKET HATS </v>
+        <v>HATS</v>
       </c>
       <c r="B71" t="str">
-        <v xml:space="preserve">  BUCKET HATS</v>
+        <v>HATS</v>
       </c>
       <c r="C71" t="str">
-        <v>588419</v>
-      </c>
-      <c r="D71" t="str">
         <v>543055</v>
       </c>
       <c r="E71" t="str">
         <v>Hoạt động</v>
       </c>
+      <c r="F71">
+        <v>7</v>
+      </c>
       <c r="G71" t="str">
         <v>Không hiển thị</v>
       </c>
       <c r="H71">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I71" t="str">
-        <v>2022-12-16 09:16:44</v>
+        <v>2024-01-17 16:16:29</v>
       </c>
       <c r="J71" t="str">
-        <v>/bucket-hats-pc588419.html</v>
+        <v>/hats-pc543055.html</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>ACCESSORIES</v>
+        <v xml:space="preserve">  BALL CAPS </v>
       </c>
       <c r="B72" t="str">
-        <v>ACCESSORIES</v>
+        <v xml:space="preserve">  BALL CAPS</v>
       </c>
       <c r="C72" t="str">
-        <v>513821</v>
+        <v>588418</v>
+      </c>
+      <c r="D72" t="str">
+        <v>543055</v>
       </c>
       <c r="E72" t="str">
         <v>Hoạt động</v>
       </c>
-      <c r="F72">
-        <v>8</v>
-      </c>
       <c r="G72" t="str">
         <v>Không hiển thị</v>
       </c>
+      <c r="H72">
+        <v>38</v>
+      </c>
       <c r="I72" t="str">
-        <v>2021-05-20 10:28:53</v>
+        <v>2022-12-16 09:16:06</v>
       </c>
       <c r="J72" t="str">
-        <v>/accessories-pc513821.html</v>
+        <v>/ball-caps-pc588418.html</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v xml:space="preserve">  SOCKS</v>
+        <v xml:space="preserve">  BUCKET HATS </v>
       </c>
       <c r="B73" t="str">
-        <v xml:space="preserve">  SOCKS</v>
+        <v xml:space="preserve">  BUCKET HATS</v>
       </c>
       <c r="C73" t="str">
-        <v>588422</v>
+        <v>588419</v>
       </c>
       <c r="D73" t="str">
-        <v>513821</v>
+        <v>543055</v>
       </c>
       <c r="E73" t="str">
         <v>Hoạt động</v>
@@ -2492,42 +2495,39 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H73">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="I73" t="str">
-        <v>2024-01-17 16:16:52</v>
+        <v>2022-12-16 09:16:44</v>
       </c>
       <c r="J73" t="str">
-        <v>/socks-pc588422.html</v>
+        <v>/bucket-hats-pc588419.html</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v xml:space="preserve">  CHARM</v>
+        <v>ACCESSORIES</v>
       </c>
       <c r="B74" t="str">
-        <v xml:space="preserve">  CHARM</v>
+        <v>ACCESSORIES</v>
       </c>
       <c r="C74" t="str">
-        <v>591307</v>
-      </c>
-      <c r="D74" t="str">
         <v>513821</v>
       </c>
       <c r="E74" t="str">
         <v>Hoạt động</v>
       </c>
+      <c r="F74">
+        <v>8</v>
+      </c>
       <c r="G74" t="str">
         <v>Không hiển thị</v>
       </c>
-      <c r="H74">
-        <v>8</v>
-      </c>
       <c r="I74" t="str">
-        <v>2024-10-15 16:32:30</v>
+        <v>2021-05-20 10:28:53</v>
       </c>
       <c r="J74" t="str">
-        <v>/charm-pc591307.html</v>
+        <v>/accessories-pc513821.html</v>
       </c>
     </row>
     <row r="75">
@@ -2561,13 +2561,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v xml:space="preserve">  BRACELETS </v>
+        <v xml:space="preserve">  CHARM</v>
       </c>
       <c r="B76" t="str">
-        <v xml:space="preserve">  BRACELETS</v>
+        <v xml:space="preserve">  CHARM</v>
       </c>
       <c r="C76" t="str">
-        <v>588423</v>
+        <v>591307</v>
       </c>
       <c r="D76" t="str">
         <v>513821</v>
@@ -2575,31 +2575,31 @@
       <c r="E76" t="str">
         <v>Hoạt động</v>
       </c>
-      <c r="F76">
-        <v>10</v>
-      </c>
       <c r="G76" t="str">
         <v>Không hiển thị</v>
       </c>
+      <c r="H76">
+        <v>8</v>
+      </c>
       <c r="I76" t="str">
-        <v>2022-12-16 09:21:03</v>
+        <v>2024-10-15 16:32:30</v>
       </c>
       <c r="J76" t="str">
-        <v>/bracelets-pc588423.html</v>
+        <v>/charm-pc591307.html</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v xml:space="preserve">    RASTACLAT </v>
+        <v xml:space="preserve">  SOCKS</v>
       </c>
       <c r="B77" t="str">
-        <v xml:space="preserve">    RASTACLAT</v>
+        <v xml:space="preserve">  SOCKS</v>
       </c>
       <c r="C77" t="str">
-        <v>588424</v>
+        <v>588422</v>
       </c>
       <c r="D77" t="str">
-        <v>588423</v>
+        <v>513821</v>
       </c>
       <c r="E77" t="str">
         <v>Hoạt động</v>
@@ -2608,24 +2608,24 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H77">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I77" t="str">
-        <v>2022-12-16 09:21:49</v>
+        <v>2024-01-17 16:16:52</v>
       </c>
       <c r="J77" t="str">
-        <v>/rastaclat-pc588424.html</v>
+        <v>/socks-pc588422.html</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v xml:space="preserve">  UPPER</v>
+        <v xml:space="preserve">  BRACELETS </v>
       </c>
       <c r="B78" t="str">
-        <v xml:space="preserve">  UPPER</v>
+        <v xml:space="preserve">  BRACELETS</v>
       </c>
       <c r="C78" t="str">
-        <v>588420</v>
+        <v>588423</v>
       </c>
       <c r="D78" t="str">
         <v>513821</v>
@@ -2633,51 +2633,109 @@
       <c r="E78" t="str">
         <v>Hoạt động</v>
       </c>
+      <c r="F78">
+        <v>10</v>
+      </c>
       <c r="G78" t="str">
         <v>Không hiển thị</v>
       </c>
-      <c r="H78">
-        <v>217</v>
-      </c>
       <c r="I78" t="str">
-        <v>2023-01-12 15:17:23</v>
+        <v>2022-12-16 09:21:03</v>
       </c>
       <c r="J78" t="str">
-        <v>/upper-pc588420.html</v>
+        <v>/bracelets-pc588423.html</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
+        <v xml:space="preserve">    RASTACLAT </v>
+      </c>
+      <c r="B79" t="str">
+        <v xml:space="preserve">    RASTACLAT</v>
+      </c>
+      <c r="C79" t="str">
+        <v>588424</v>
+      </c>
+      <c r="D79" t="str">
+        <v>588423</v>
+      </c>
+      <c r="E79" t="str">
+        <v>Hoạt động</v>
+      </c>
+      <c r="G79" t="str">
+        <v>Không hiển thị</v>
+      </c>
+      <c r="H79">
+        <v>36</v>
+      </c>
+      <c r="I79" t="str">
+        <v>2022-12-16 09:21:49</v>
+      </c>
+      <c r="J79" t="str">
+        <v>/rastaclat-pc588424.html</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v xml:space="preserve">  UPPER</v>
+      </c>
+      <c r="B80" t="str">
+        <v xml:space="preserve">  UPPER</v>
+      </c>
+      <c r="C80" t="str">
+        <v>588420</v>
+      </c>
+      <c r="D80" t="str">
+        <v>513821</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Hoạt động</v>
+      </c>
+      <c r="G80" t="str">
+        <v>Không hiển thị</v>
+      </c>
+      <c r="H80">
+        <v>217</v>
+      </c>
+      <c r="I80" t="str">
+        <v>2023-01-12 15:17:23</v>
+      </c>
+      <c r="J80" t="str">
+        <v>/upper-pc588420.html</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
         <v>T-SHIRTS</v>
       </c>
-      <c r="B79" t="str">
+      <c r="B81" t="str">
         <v>T-SHIRTS</v>
       </c>
-      <c r="C79" t="str">
+      <c r="C81" t="str">
         <v>543058</v>
       </c>
-      <c r="E79" t="str">
-        <v>Hoạt động</v>
-      </c>
-      <c r="F79">
+      <c r="E81" t="str">
+        <v>Hoạt động</v>
+      </c>
+      <c r="F81">
         <v>9</v>
       </c>
-      <c r="G79" t="str">
-        <v>Không hiển thị</v>
-      </c>
-      <c r="H79">
+      <c r="G81" t="str">
+        <v>Không hiển thị</v>
+      </c>
+      <c r="H81">
         <v>33</v>
       </c>
-      <c r="I79" t="str">
+      <c r="I81" t="str">
         <v>2024-01-17 16:17:13</v>
       </c>
-      <c r="J79" t="str">
+      <c r="J81" t="str">
         <v>/tshirts-pc543058.html</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J79"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J81"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/categories_dump.xlsx
+++ b/categories_dump.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name=" 2026-01-05" sheetId="1" r:id="rId1"/>
+    <sheet name=" 2026-01-15" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -2579,7 +2579,7 @@
         <v>Không hiển thị</v>
       </c>
       <c r="H76">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I76" t="str">
         <v>2024-10-15 16:32:30</v>
